--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487698_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487698_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9856</v>
+        <v>4.7486</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9217</v>
+        <v>4.6029</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0639</v>
+        <v>0.1457</v>
       </c>
       <c r="G2" t="n">
         <v>3.5104</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.535</v>
+        <v>1.2979</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2146</v>
+        <v>0.8958</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3203</v>
+        <v>0.4021</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2239</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.917</v>
+        <v>4.4258</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6661</v>
+        <v>3.9295</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2509</v>
+        <v>0.4963</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1593</v>
+        <v>0.6439</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3874</v>
+        <v>-0.8642</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7719</v>
+        <v>1.5082</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9564</v>
+        <v>2.0092</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3068</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6495</v>
+        <v>1.9309</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7971</v>
+        <v>-1.3652</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9195</v>
+        <v>-0.9425</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1223</v>
+        <v>-0.4227</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3582</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9105</v>
+        <v>-2.3284</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8921</v>
+        <v>-0.2972</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3963</v>
+        <v>-0.0348</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4958</v>
+        <v>-0.2624</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2239</v>
+        <v>4.6612</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2239</v>
+        <v>4.2836</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7885</v>
+        <v>2.5434</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1287</v>
+        <v>1.565</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6598000000000001</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6439</v>
+        <v>2.1593</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8642</v>
+        <v>1.3874</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5082</v>
+        <v>0.7719</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0092</v>
+        <v>2.9564</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07829999999999999</v>
+        <v>2.3068</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9309</v>
+        <v>0.6495</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3652</v>
+        <v>-0.7971</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9425</v>
+        <v>-0.9195</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4227</v>
+        <v>0.1223</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3284</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9345</v>
+        <v>0.5184</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8356</v>
+        <v>0.2952</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0989</v>
+        <v>0.2232</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6612</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>4.2836</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7084</v>
+        <v>1.7178</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0682</v>
+        <v>0.132</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7765</v>
+        <v>1.5857</v>
       </c>
       <c r="G5" t="n">
         <v>0.9147</v>
@@ -844,13 +844,13 @@
         <v>0.9702</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1765</v>
+        <v>-0.1671</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1211</v>
+        <v>0.0791</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0554</v>
+        <v>-0.2462</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5534</v>
+        <v>0.5272</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9854000000000001</v>
+        <v>-0.2264</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.7536</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.706</v>
+        <v>-2.3188</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8809</v>
+        <v>-3.0211</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.8251</v>
+        <v>0.7024</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.624</v>
+        <v>-1.8666</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.622</v>
+        <v>-1.9072</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.002</v>
+        <v>0.0406</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.082</v>
+        <v>-0.4521</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2589</v>
+        <v>-1.1139</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8231000000000001</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>1.3582</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1236</v>
+        <v>0.2638</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0154</v>
+        <v>0.4164</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1081</v>
+        <v>-0.1525</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7776</v>
+        <v>1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>1.788</v>
+        <v>1.2239</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.421</v>
+        <v>0.5068</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3871</v>
+        <v>-0.1157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8081</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.3188</v>
+        <v>-4.706</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.0211</v>
+        <v>-1.8809</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7024</v>
+        <v>-2.8251</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8666</v>
+        <v>-2.624</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.9072</v>
+        <v>-0.622</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>-2.002</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4521</v>
+        <v>-2.082</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1139</v>
+        <v>-1.2589</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6618000000000001</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P7" t="n">
         <v>1.3582</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1577</v>
+        <v>1.077</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2557</v>
+        <v>0.9143</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.098</v>
+        <v>0.1626</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2239</v>
+        <v>2.7776</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2239</v>
+        <v>1.788</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.9896</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3188</v>
+        <v>0.2308</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1773</v>
+        <v>-0.1563</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4961</v>
+        <v>0.3871</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7396</v>
@@ -1078,13 +1078,13 @@
         <v>1.7463</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3883</v>
+        <v>0.3003</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5596</v>
+        <v>0.5807</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1713</v>
+        <v>-0.2804</v>
       </c>
       <c r="V8" t="n">
         <v>0.2821</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DE DOMINGO GARAY</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2288</v>
+        <v>-0.7076</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2724</v>
+        <v>-0.6097</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0436</v>
+        <v>-0.0979</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1686</v>
+        <v>1.0151</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4029</v>
+        <v>1.9666</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7658</v>
+        <v>-0.9515</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6061</v>
+        <v>0.7768</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0206</v>
+        <v>1.9897</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6267</v>
+        <v>-1.2129</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5625</v>
+        <v>0.2383</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4235</v>
+        <v>-0.0231</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.139</v>
+        <v>0.2614</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0601</v>
+        <v>0.549</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3039</v>
+        <v>0.4374</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3641</v>
+        <v>0.1116</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8836</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>J. DE DOMINGO GARAY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8808</v>
+        <v>-1.4746</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5922</v>
+        <v>-1.5727</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2886</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0151</v>
+        <v>-1.1686</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9666</v>
+        <v>-0.4029</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9515</v>
+        <v>-0.7658</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7768</v>
+        <v>-0.6061</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9897</v>
+        <v>0.0206</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2129</v>
+        <v>-0.6267</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2383</v>
+        <v>-0.5625</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0231</v>
+        <v>-0.4235</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2614</v>
+        <v>-0.139</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6243</v>
+        <v>-0.3059</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5451</v>
+        <v>0.0036</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.3095</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8836</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2676</v>
+        <v>-2.2122</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3736</v>
+        <v>-2.291</v>
       </c>
       <c r="F11" t="n">
-        <v>0.106</v>
+        <v>0.0788</v>
       </c>
       <c r="G11" t="n">
         <v>-2.4742</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5397</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7874</v>
+        <v>0.2952</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2477</v>
+        <v>0.2204</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2239</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.433</v>
+        <v>-3.5415</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2521</v>
+        <v>-0.5514</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1809</v>
+        <v>-2.9901</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7079</v>
@@ -1390,13 +1390,13 @@
         <v>1.7463</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4251</v>
+        <v>-0.5336</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6539</v>
+        <v>0.0468</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7712</v>
+        <v>-0.5804</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9418</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9852</v>
+        <v>-4.9586</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0911</v>
+        <v>-5.3098</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1059</v>
+        <v>0.3512</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8593</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4562</v>
+        <v>0.4828</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0329</v>
+        <v>0.8142</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5767</v>
+        <v>-0.3314</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8972999999999987</v>
+        <v>1.805899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.512099999999999</v>
+        <v>-0.6036000000000019</v>
       </c>
       <c r="F14" t="n">
         <v>2.4093</v>
@@ -1513,7 +1513,7 @@
         <v>-8.731000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.336599999999999</v>
+        <v>-3.336600000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-5.394299999999999</v>
@@ -1546,10 +1546,10 @@
         <v>17.463</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7927</v>
+        <v>3.701000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8353</v>
+        <v>4.7439</v>
       </c>
       <c r="U14" t="n">
         <v>-1.0429</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8044</v>
+        <v>4.2593</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0295</v>
+        <v>2.4299</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7749</v>
+        <v>1.8294</v>
       </c>
       <c r="G15" t="n">
         <v>2.654</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9708</v>
+        <v>-0.5159</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3264</v>
+        <v>0.074</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6444</v>
+        <v>-0.5899</v>
       </c>
       <c r="V15" t="n">
         <v>0.763</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1699</v>
+        <v>2.8494</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8764999999999999</v>
+        <v>1.4771</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2934</v>
+        <v>1.3724</v>
       </c>
       <c r="G16" t="n">
         <v>0.0142</v>
@@ -1702,13 +1702,13 @@
         <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8741</v>
+        <v>-0.1946</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5451</v>
+        <v>0.0555</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.329</v>
+        <v>-0.2501</v>
       </c>
       <c r="V16" t="n">
         <v>2.4477</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>C. CRESPO MONTESINOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5437</v>
+        <v>2.1105</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2189</v>
+        <v>2.5854</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6752</v>
+        <v>-0.4749</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8652</v>
+        <v>0.834</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9132</v>
+        <v>-0.767</v>
       </c>
       <c r="I17" t="n">
-        <v>0.952</v>
+        <v>1.6011</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4496</v>
+        <v>1.5814</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2873</v>
+        <v>-0.3089</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1624</v>
+        <v>1.8903</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4156</v>
+        <v>-0.7473</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.374</v>
+        <v>-0.4581</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7897</v>
+        <v>-0.2892</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-0.3881</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5336</v>
+        <v>-0.3791</v>
       </c>
       <c r="T17" t="n">
-        <v>0.729</v>
+        <v>-0.1139</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1954</v>
+        <v>-0.2652</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.4373</v>
+        <v>0.1033</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.9896</v>
+        <v>1.506</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4477</v>
+        <v>-1.4027</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. CRESPO MONTESINOS</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0766</v>
+        <v>1.2857</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9848</v>
+        <v>1.7184</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9082</v>
+        <v>-0.4328</v>
       </c>
       <c r="G18" t="n">
-        <v>0.834</v>
+        <v>3.8652</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.767</v>
+        <v>2.9132</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6011</v>
+        <v>0.952</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5814</v>
+        <v>3.4496</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3089</v>
+        <v>3.2873</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8903</v>
+        <v>0.1624</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7473</v>
+        <v>0.4156</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4581</v>
+        <v>-0.374</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2892</v>
+        <v>0.7897</v>
       </c>
       <c r="P18" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9702</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.5523</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.3881</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.9403</v>
-      </c>
       <c r="S18" t="n">
-        <v>-1.413</v>
+        <v>0.2756</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7145</v>
+        <v>0.2285</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6985</v>
+        <v>0.0471</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1033</v>
+        <v>-3.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>1.506</v>
+        <v>-0.9896</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4027</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7501</v>
+        <v>0.8319</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0586</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8087</v>
+        <v>0.8904</v>
       </c>
       <c r="G19" t="n">
         <v>1.2152</v>
@@ -1936,13 +1936,13 @@
         <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2607</v>
+        <v>-0.1789</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0482</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V19" t="n">
         <v>0.3776</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6262</v>
+        <v>0.4077</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4131</v>
+        <v>1.1128</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7869</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0.353</v>
@@ -2014,13 +2014,13 @@
         <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.07920000000000001</v>
+        <v>-0.1394</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4251</v>
+        <v>0.1248</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3459</v>
+        <v>-0.2641</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6153</v>
+        <v>0.0593</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0804</v>
+        <v>1.2507</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4651</v>
+        <v>-1.1914</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0976</v>
+        <v>3.0773</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5232</v>
+        <v>0.9952</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5745</v>
+        <v>2.0821</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1322</v>
+        <v>2.3112</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0916</v>
+        <v>1.0298</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0406</v>
+        <v>1.2813</v>
       </c>
       <c r="M21" t="n">
+        <v>0.7662</v>
+      </c>
+      <c r="N21" t="n">
         <v>-0.0346</v>
       </c>
-      <c r="N21" t="n">
-        <v>-0.5685</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.5339</v>
+        <v>0.8008</v>
       </c>
       <c r="P21" t="n">
         <v>-0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5953</v>
+        <v>-0.3763</v>
       </c>
       <c r="T21" t="n">
-        <v>1.578</v>
+        <v>0.1037</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0173</v>
+        <v>-0.48</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8836</v>
+        <v>-2.4477</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2624</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6331</v>
+        <v>-0.4329</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3708</v>
+        <v>0.3435</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6199</v>
@@ -2170,13 +2170,13 @@
         <v>0.5821</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2245</v>
+        <v>-0.0516</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1088</v>
+        <v>0.0914</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3044</v>
+        <v>-0.4341</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0505</v>
+        <v>-0.0207</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3549</v>
+        <v>-0.4134</v>
       </c>
       <c r="G23" t="n">
-        <v>3.0773</v>
+        <v>1.0976</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9952</v>
+        <v>0.5232</v>
       </c>
       <c r="I23" t="n">
-        <v>2.0821</v>
+        <v>0.5745</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3112</v>
+        <v>1.1322</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0298</v>
+        <v>1.0916</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2813</v>
+        <v>0.0406</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7662</v>
+        <v>-0.0346</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0346</v>
+        <v>-0.5685</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8008</v>
+        <v>0.5339</v>
       </c>
       <c r="P23" t="n">
         <v>-0.194</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.74</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0965</v>
+        <v>0.4769</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6435</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4477</v>
+        <v>-1.8836</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0361</v>
+        <v>-2.1817</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9393</v>
+        <v>-2.1395</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.0422</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1028</v>
@@ -2326,13 +2326,13 @@
         <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2306</v>
+        <v>-0.3763</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2804</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.511</v>
+        <v>-0.4564</v>
       </c>
       <c r="V24" t="n">
         <v>0.1033</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1793</v>
+        <v>-4.2455</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9696</v>
+        <v>-5.2699</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7904</v>
+        <v>1.0244</v>
       </c>
       <c r="G25" t="n">
         <v>0.7282</v>
@@ -2404,13 +2404,13 @@
         <v>2.1344</v>
       </c>
       <c r="S25" t="n">
-        <v>1.1804</v>
+        <v>0.1141</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4991</v>
+        <v>0.1988</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6813</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0.1511</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7015</v>
+        <v>-5.0831</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.4624</v>
+        <v>-5.062</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2392</v>
+        <v>-0.0211</v>
       </c>
       <c r="G26" t="n">
         <v>-2.3851</v>
@@ -2482,13 +2482,13 @@
         <v>1.7463</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4675</v>
+        <v>-0.849</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6292</v>
+        <v>-0.2288</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-0.6202</v>
       </c>
       <c r="V26" t="n">
         <v>-1.0728</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.8974999999999982</v>
+        <v>-0.2300000000000022</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.409299999999999</v>
+        <v>-2.409300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>1.512</v>
+        <v>2.1792</v>
       </c>
       <c r="G27" t="n">
         <v>8.7309</v>
@@ -2539,10 +2539,10 @@
         <v>7.1925</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5018</v>
+        <v>1.501800000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0367</v>
+        <v>0.03670000000000002</v>
       </c>
       <c r="N27" t="n">
         <v>-3.8559</v>
@@ -2560,13 +2560,13 @@
         <v>15.5227</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.7927</v>
+        <v>-2.1255</v>
       </c>
       <c r="T27" t="n">
         <v>1.0429</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.8354</v>
+        <v>-3.1681</v>
       </c>
       <c r="V27" t="n">
         <v>-4.8954</v>
